--- a/Modules/PanVCA/PanVCA_BOM.xlsx
+++ b/Modules/PanVCA/PanVCA_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\_wip\PanVCA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\PanVCA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D52515-1A2E-4798-B078-48C9D5C81F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8132046-FC47-4DEF-88FD-FDAAB0164301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -89,15 +89,9 @@
     <t>Pushernut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Jack Nut</t>
   </si>
   <si>
@@ -224,9 +218,6 @@
     <t>https://www.tme.eu/de/en/details/l-937egw/tht-leds-3mm/kingbright-electronic/</t>
   </si>
   <si>
-    <t>https://www.tme.eu/de/en/details/zl202-80g/pin-headers/connfly/ds1021-2-40sf11/</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <u/>
@@ -980,6 +971,15 @@
       </rPr>
       <t>**</t>
     </r>
+  </si>
+  <si>
+    <t>https://www.tme.eu/de/en/details/zl202-10g/pin-headers/connfly/ds1021-2-5sf11-b/</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
   </si>
 </sst>
 </file>
@@ -1902,7 +1902,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1937,19 +1937,19 @@
         <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1960,19 +1960,19 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="J4" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1983,19 +1983,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -2003,22 +2003,22 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" t="s">
         <v>61</v>
       </c>
-      <c r="C6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" t="s">
-        <v>64</v>
-      </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -2026,22 +2026,22 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -2049,22 +2049,22 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -2072,22 +2072,22 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -2098,19 +2098,19 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -2118,22 +2118,22 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -2141,22 +2141,22 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" t="s">
         <v>68</v>
       </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" t="s">
-        <v>71</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -2167,19 +2167,19 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" t="s">
-        <v>85</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="J13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -2190,19 +2190,19 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -2210,22 +2210,22 @@
         <v>2</v>
       </c>
       <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="J15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -2233,22 +2233,22 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2256,22 +2256,22 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E17" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -2279,22 +2279,22 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" t="s">
         <v>99</v>
       </c>
-      <c r="D18" t="s">
-        <v>102</v>
-      </c>
       <c r="E18" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2302,22 +2302,22 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" t="s">
+        <v>102</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C19" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" t="s">
-        <v>105</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="J19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2325,22 +2325,22 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2348,22 +2348,22 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2371,22 +2371,22 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" t="s">
         <v>26</v>
       </c>
-      <c r="C22" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" t="s">
-        <v>28</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2394,22 +2394,22 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C23" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="E23" t="s">
-        <v>111</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="J23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2417,22 +2417,22 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E24" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2440,13 +2440,13 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
         <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E25" t="s">
         <v>12</v>
@@ -2455,7 +2455,7 @@
         <v>15</v>
       </c>
       <c r="J25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2463,10 +2463,10 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -2475,10 +2475,10 @@
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>55</v>
+        <v>122</v>
       </c>
       <c r="J26" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2495,13 +2495,13 @@
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="J28" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2509,19 +2509,19 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C29" t="s">
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="J29" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2532,16 +2532,16 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2549,19 +2549,19 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" t="s">
         <v>39</v>
       </c>
-      <c r="C31" t="s">
+      <c r="F31" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E31" t="s">
-        <v>41</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="J31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -2569,7 +2569,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B33" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2577,12 +2577,12 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -2594,33 +2594,33 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F25" r:id="rId1" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F28" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="F29" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="F22" r:id="rId4" xr:uid="{0D90FBA3-232B-45F3-9B80-144E63D03E3D}"/>
-    <hyperlink ref="F20" r:id="rId5" xr:uid="{8DF1F044-558D-44D8-8070-099BFF365FAB}"/>
-    <hyperlink ref="F31" r:id="rId6" xr:uid="{D0673C57-FA09-40F3-A004-4F5B32DB700F}"/>
-    <hyperlink ref="F16" r:id="rId7" xr:uid="{A73CC50D-6402-4B9F-BA89-B7BEF6A9A237}"/>
-    <hyperlink ref="F26" r:id="rId8" xr:uid="{E60A799E-C70E-4656-8426-1D272A3F13D2}"/>
-    <hyperlink ref="F30" r:id="rId9" xr:uid="{4F25721E-C4C9-49DB-97FF-D9D5C33601A0}"/>
-    <hyperlink ref="F21" r:id="rId10" xr:uid="{360AA49B-942A-4136-9898-3D7645969441}"/>
-    <hyperlink ref="F3" r:id="rId11" xr:uid="{5D2D33A0-9624-4E40-8A6D-7B21B5E2FF47}"/>
-    <hyperlink ref="F6" r:id="rId12" xr:uid="{5CAA8150-CF20-4CFE-A840-CA8C1C89BF7E}"/>
-    <hyperlink ref="F7" r:id="rId13" xr:uid="{25157632-8A6D-4D25-8A0E-965480D99504}"/>
-    <hyperlink ref="F8" r:id="rId14" xr:uid="{619FAB32-4CCD-42CB-94B4-6EB80F0DE422}"/>
-    <hyperlink ref="F9" r:id="rId15" xr:uid="{E12B3A5F-C561-46DC-BCED-F937BF8C4ADF}"/>
-    <hyperlink ref="F4" r:id="rId16" xr:uid="{896385C2-7ABE-4EB0-89E1-98F54578B8C7}"/>
-    <hyperlink ref="F5" r:id="rId17" xr:uid="{375651E5-3718-4B16-BCCC-41AA370EBAAD}"/>
-    <hyperlink ref="F10" r:id="rId18" xr:uid="{160CC318-6CB6-4D31-A6EB-6B6FFEB474AA}"/>
-    <hyperlink ref="F11" r:id="rId19" xr:uid="{E0B7E817-EB51-4765-B956-B74B3DB8CC95}"/>
-    <hyperlink ref="F12" r:id="rId20" xr:uid="{A6FEF9B1-4ED5-493E-9395-5074C43A997C}"/>
-    <hyperlink ref="F18" r:id="rId21" xr:uid="{B108C37C-865F-4C15-9D54-D6C90D74D0B4}"/>
-    <hyperlink ref="F14" r:id="rId22" xr:uid="{F6A055C4-84A9-4465-9215-98F897F31E5D}"/>
-    <hyperlink ref="F13" r:id="rId23" xr:uid="{B94571EC-5C16-4853-9334-A72E077FF6DE}"/>
-    <hyperlink ref="F15" r:id="rId24" xr:uid="{0A5D2E17-AF00-4333-B283-200938D533EB}"/>
-    <hyperlink ref="F17" r:id="rId25" xr:uid="{403166A3-E13F-456E-AD96-AE3FF75A2C96}"/>
-    <hyperlink ref="F19" r:id="rId26" xr:uid="{ED5119AB-1AE3-4B2D-8862-A582C52FD583}"/>
-    <hyperlink ref="F23" r:id="rId27" xr:uid="{856A7AE4-88A0-4323-B7E2-1401F60049E4}"/>
-    <hyperlink ref="F24" r:id="rId28" xr:uid="{C5C646A6-5040-43C1-B98B-858D85F31260}"/>
+    <hyperlink ref="F22" r:id="rId2" xr:uid="{0D90FBA3-232B-45F3-9B80-144E63D03E3D}"/>
+    <hyperlink ref="F20" r:id="rId3" xr:uid="{8DF1F044-558D-44D8-8070-099BFF365FAB}"/>
+    <hyperlink ref="F31" r:id="rId4" xr:uid="{D0673C57-FA09-40F3-A004-4F5B32DB700F}"/>
+    <hyperlink ref="F16" r:id="rId5" xr:uid="{A73CC50D-6402-4B9F-BA89-B7BEF6A9A237}"/>
+    <hyperlink ref="F30" r:id="rId6" xr:uid="{4F25721E-C4C9-49DB-97FF-D9D5C33601A0}"/>
+    <hyperlink ref="F21" r:id="rId7" xr:uid="{360AA49B-942A-4136-9898-3D7645969441}"/>
+    <hyperlink ref="F3" r:id="rId8" xr:uid="{5D2D33A0-9624-4E40-8A6D-7B21B5E2FF47}"/>
+    <hyperlink ref="F6" r:id="rId9" xr:uid="{5CAA8150-CF20-4CFE-A840-CA8C1C89BF7E}"/>
+    <hyperlink ref="F7" r:id="rId10" xr:uid="{25157632-8A6D-4D25-8A0E-965480D99504}"/>
+    <hyperlink ref="F8" r:id="rId11" xr:uid="{619FAB32-4CCD-42CB-94B4-6EB80F0DE422}"/>
+    <hyperlink ref="F9" r:id="rId12" xr:uid="{E12B3A5F-C561-46DC-BCED-F937BF8C4ADF}"/>
+    <hyperlink ref="F4" r:id="rId13" xr:uid="{896385C2-7ABE-4EB0-89E1-98F54578B8C7}"/>
+    <hyperlink ref="F5" r:id="rId14" xr:uid="{375651E5-3718-4B16-BCCC-41AA370EBAAD}"/>
+    <hyperlink ref="F10" r:id="rId15" xr:uid="{160CC318-6CB6-4D31-A6EB-6B6FFEB474AA}"/>
+    <hyperlink ref="F11" r:id="rId16" xr:uid="{E0B7E817-EB51-4765-B956-B74B3DB8CC95}"/>
+    <hyperlink ref="F12" r:id="rId17" xr:uid="{A6FEF9B1-4ED5-493E-9395-5074C43A997C}"/>
+    <hyperlink ref="F18" r:id="rId18" xr:uid="{B108C37C-865F-4C15-9D54-D6C90D74D0B4}"/>
+    <hyperlink ref="F14" r:id="rId19" xr:uid="{F6A055C4-84A9-4465-9215-98F897F31E5D}"/>
+    <hyperlink ref="F13" r:id="rId20" xr:uid="{B94571EC-5C16-4853-9334-A72E077FF6DE}"/>
+    <hyperlink ref="F15" r:id="rId21" xr:uid="{0A5D2E17-AF00-4333-B283-200938D533EB}"/>
+    <hyperlink ref="F17" r:id="rId22" xr:uid="{403166A3-E13F-456E-AD96-AE3FF75A2C96}"/>
+    <hyperlink ref="F19" r:id="rId23" xr:uid="{ED5119AB-1AE3-4B2D-8862-A582C52FD583}"/>
+    <hyperlink ref="F23" r:id="rId24" xr:uid="{856A7AE4-88A0-4323-B7E2-1401F60049E4}"/>
+    <hyperlink ref="F24" r:id="rId25" xr:uid="{C5C646A6-5040-43C1-B98B-858D85F31260}"/>
+    <hyperlink ref="F26" r:id="rId26" xr:uid="{6A6D3754-27B4-49A4-8C38-F40458AB01F9}"/>
+    <hyperlink ref="F28" r:id="rId27" xr:uid="{2451FDE8-BA03-4163-A94A-A48BF9FB78AB}"/>
+    <hyperlink ref="F29" r:id="rId28" xr:uid="{0ED9C294-C6F1-460F-9AAE-4D60EDEEF086}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
